--- a/qaFHIRErrors/ig/observations-summary.xlsx
+++ b/qaFHIRErrors/ig/observations-summary.xlsx
@@ -179,7 +179,7 @@
     <t>Observation Category Codes#social-history</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-social-history-code-cisis|20260619134042 (required)</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-social-history-code-cisis|20260716085852 (required)</t>
   </si>
   <si>
     <t>fr-observation-vital-signs-document</t>
@@ -191,7 +191,7 @@
     <t>Observation Category Codes#vital-signs</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-signe-vital-cisis|20260619134043 (required)</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-signe-vital-cisis|20260716085853 (required)</t>
   </si>
   <si>
     <t>fr-observation-vital-signs-panel-document</t>
